--- a/data/trans_orig/IP16A112_2023R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A112_2023R-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39605</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27968</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>37807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61039</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39187</t>
+          <t>39521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69604</t>
+          <t>69427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72133</t>
+          <t>71168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109714</t>
+          <t>110670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>19319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,26%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41967</t>
+          <t>43991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90853</t>
+          <t>89708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66408</t>
+          <t>67734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91666</t>
+          <t>91701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113618</t>
+          <t>116757</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172523</t>
+          <t>173112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86171</t>
+          <t>87316</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135057</t>
+          <t>133033</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88151</t>
+          <t>88116</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>113409</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>184318</t>
+          <t>183729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243223</t>
+          <t>240084</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
